--- a/templates/finance-brain/examples/workpapers/2101 - Accrued Expenses - Usage Accrual 2026.09.xlsx
+++ b/templates/finance-brain/examples/workpapers/2101 - Accrued Expenses - Usage Accrual 2026.09.xlsx
@@ -56,10 +56,10 @@
     <t xml:space="preserve">handbook/accounting-policies.md, Accruals: accrue unbilled expenses over $2,500; reverse on the first day of the next month.</t>
   </si>
   <si>
-    <t xml:space="preserve">Command</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commands/jes/usage-accrual.md</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skills/usage-accrual/</t>
   </si>
   <si>
     <t xml:space="preserve">Result</t>
